--- a/Proiect/Proiect/Output/Rapoarte/Rezultate_Prognoza.xlsx
+++ b/Proiect/Proiect/Output/Rapoarte/Rezultate_Prognoza.xlsx
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Furturi_Previzionate</t>
+          <t>Furturi_Estimat</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -379,17 +379,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Criza Economica (Somaj +50%, PIB -20%)</t>
+          <t>Criza Economica</t>
         </is>
       </c>
       <c r="B2">
-        <v>44714.10289951871</v>
+        <v>40737.68611542839</v>
       </c>
       <c r="C2">
-        <v>10853.73258677735</v>
+        <v>21278.28910441763</v>
       </c>
       <c r="D2">
-        <v>184208.6104594536</v>
+        <v>77993.06898667067</v>
       </c>
     </row>
   </sheetData>
